--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6801.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6801.xlsx
@@ -9813,9 +9813,27 @@
       <c r="D95" t="n">
         <v>0.75</v>
       </c>
+      <c r="E95" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="F95" t="n">
+        <v>60</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.2837</v>
+      </c>
       <c r="H95" t="n">
         <v>0.659</v>
       </c>
+      <c r="I95" t="n">
+        <v>0.0984</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="K95" t="n">
+        <v>37</v>
+      </c>
       <c r="L95" t="n">
         <v>0.4375</v>
       </c>
@@ -9849,12 +9867,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: D1@BORE, D2@BORE, HEXB@HEX, JIC_CONEDIA@DRIVE, LEG_JIC@DRIVE, LEG_ORB@DRIVE, ORB_GRVDIA@DRIVE, ORB_I3@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE, Y@REF] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6801-08-04-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: D1@BORE, D2@BORE, HEXB@HEX, JIC_CONEDIA@DRIVE, LEG_JIC@DRIVE, LEG_ORB@DRIVE, ORB_GRVDIA@DRIVE, ORB_I3@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE, Y@REF, JIC_RELIEFL@DRIVE, RELIEFANG@DRIVE, JIC_THDZ@DRIVE, JIC_LANDL@DRIVE, JIC_SEATL@DRIVE, SEATB@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6801-08-04-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6801-08-04-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6801-08-04-NWO-FG (PARTcommunity / CADENAS, D1@BORE=B1D, D2@BORE=B2D, HEXB@HEX=C, JIC_CONEDIA@DRIVE=AL, LEG_JIC@DRIVE=M, LEG_ORB@DRIVE=M7, ORB_GRVDIA@DRIVE=HT, ORB_I3@DRIVE=GT, THDMAJ_A@DRIVE=B1THD, THDMAJ_B@DRIVE=B2THD, Y@REF=Y; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6801-08-04-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6801-08-04-NWO-FG (PARTcommunity / CADENAS, D1@BORE=B1D, D2@BORE=B2D, HEXB@HEX=C, JIC_CONEDIA@DRIVE=AL, LEG_JIC@DRIVE=M, LEG_ORB@DRIVE=M7, ORB_GRVDIA@DRIVE=HT, ORB_I3@DRIVE=GT, THDMAJ_A@DRIVE=B1THD, THDMAJ_B@DRIVE=B2THD, Y@REF=Y, JIC_RELIEFL@DRIVE=ENDLIB, RELIEFANG@DRIVE=ENDLIB, JIC_THDZ@DRIVE=ENDLIB, JIC_LANDL@DRIVE=ENDLIB, JIC_SEATL@DRIVE=ENDLIB, SEATB@DRIVE=ENDLIB; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
@@ -9888,9 +9906,27 @@
       <c r="D96" t="n">
         <v>0.75</v>
       </c>
+      <c r="E96" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="F96" t="n">
+        <v>60</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.2837</v>
+      </c>
       <c r="H96" t="n">
         <v>0.659</v>
       </c>
+      <c r="I96" t="n">
+        <v>0.0984</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="K96" t="n">
+        <v>37</v>
+      </c>
       <c r="L96" t="n">
         <v>1.3125</v>
       </c>
@@ -9924,12 +9960,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: D1@BORE, D2@BORE, HEXB@HEX, JIC_CONEDIA@DRIVE, LEG_JIC@DRIVE, LEG_ORB@DRIVE, ORB_GRVDIA@DRIVE, ORB_I3@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE, Y@REF] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6801-08-16-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: D1@BORE, D2@BORE, HEXB@HEX, JIC_CONEDIA@DRIVE, LEG_JIC@DRIVE, LEG_ORB@DRIVE, ORB_GRVDIA@DRIVE, ORB_I3@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE, Y@REF, JIC_RELIEFL@DRIVE, RELIEFANG@DRIVE, JIC_THDZ@DRIVE, JIC_LANDL@DRIVE, JIC_SEATL@DRIVE, SEATB@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6801-08-16-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6801-08-16-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6801-08-16-NWO-FG (PARTcommunity / CADENAS, D1@BORE=B1D, D2@BORE=B2D, HEXB@HEX=C, JIC_CONEDIA@DRIVE=AL, LEG_JIC@DRIVE=M, LEG_ORB@DRIVE=M7, ORB_GRVDIA@DRIVE=HT, ORB_I3@DRIVE=GT, THDMAJ_A@DRIVE=B1THD, THDMAJ_B@DRIVE=B2THD, Y@REF=Y; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6801-08-16-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6801-08-16-NWO-FG (PARTcommunity / CADENAS, D1@BORE=B1D, D2@BORE=B2D, HEXB@HEX=C, JIC_CONEDIA@DRIVE=AL, LEG_JIC@DRIVE=M, LEG_ORB@DRIVE=M7, ORB_GRVDIA@DRIVE=HT, ORB_I3@DRIVE=GT, THDMAJ_A@DRIVE=B1THD, THDMAJ_B@DRIVE=B2THD, Y@REF=Y, JIC_RELIEFL@DRIVE=ENDLIB, RELIEFANG@DRIVE=ENDLIB, JIC_THDZ@DRIVE=ENDLIB, JIC_LANDL@DRIVE=ENDLIB, JIC_SEATL@DRIVE=ENDLIB, SEATB@DRIVE=ENDLIB; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
@@ -9963,9 +9999,27 @@
       <c r="D97" t="n">
         <v>1.0625</v>
       </c>
+      <c r="E97" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F97" t="n">
+        <v>60</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.3895</v>
+      </c>
       <c r="H97" t="n">
         <v>0.9429999999999999</v>
       </c>
+      <c r="I97" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="K97" t="n">
+        <v>37</v>
+      </c>
       <c r="L97" t="n">
         <v>1.625</v>
       </c>
@@ -9999,12 +10053,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: D1@BORE, D2@BORE, HEXB@HEX, JIC_CONEDIA@DRIVE, LEG_JIC@DRIVE, LEG_ORB@DRIVE, ORB_GRVDIA@DRIVE, ORB_I3@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE, Y@REF] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6801-12-20-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: D1@BORE, D2@BORE, HEXB@HEX, JIC_CONEDIA@DRIVE, LEG_JIC@DRIVE, LEG_ORB@DRIVE, ORB_GRVDIA@DRIVE, ORB_I3@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE, Y@REF, JIC_RELIEFL@DRIVE, RELIEFANG@DRIVE, JIC_THDZ@DRIVE, JIC_LANDL@DRIVE, JIC_SEATL@DRIVE, SEATB@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6801-12-20-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6801-12-20-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6801-12-20-NWO-FG (PARTcommunity / CADENAS, D1@BORE=B1D, D2@BORE=B2D, HEXB@HEX=C, JIC_CONEDIA@DRIVE=AL, LEG_JIC@DRIVE=M, LEG_ORB@DRIVE=M7, ORB_GRVDIA@DRIVE=HT, ORB_I3@DRIVE=GT, THDMAJ_A@DRIVE=B1THD, THDMAJ_B@DRIVE=B2THD, Y@REF=Y; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6801-12-20-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6801-12-20-NWO-FG (PARTcommunity / CADENAS, D1@BORE=B1D, D2@BORE=B2D, HEXB@HEX=C, JIC_CONEDIA@DRIVE=AL, LEG_JIC@DRIVE=M, LEG_ORB@DRIVE=M7, ORB_GRVDIA@DRIVE=HT, ORB_I3@DRIVE=GT, THDMAJ_A@DRIVE=B1THD, THDMAJ_B@DRIVE=B2THD, Y@REF=Y, JIC_RELIEFL@DRIVE=ENDLIB, RELIEFANG@DRIVE=ENDLIB, JIC_THDZ@DRIVE=ENDLIB, JIC_LANDL@DRIVE=ENDLIB, JIC_SEATL@DRIVE=ENDLIB, SEATB@DRIVE=ENDLIB; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
@@ -10142,9 +10196,27 @@
       <c r="D99" t="n">
         <v>1.3125</v>
       </c>
+      <c r="E99" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F99" t="n">
+        <v>60</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.4365</v>
+      </c>
       <c r="H99" t="n">
         <v>1.193</v>
       </c>
+      <c r="I99" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="K99" t="n">
+        <v>37</v>
+      </c>
       <c r="L99" t="n">
         <v>1.875</v>
       </c>
@@ -10178,12 +10250,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: D1@BORE, D2@BORE, HEXB@HEX, JIC_CONEDIA@DRIVE, LEG_JIC@DRIVE, LEG_ORB@DRIVE, ORB_GRVDIA@DRIVE, ORB_I3@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE, Y@REF] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6801-16-24-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: D1@BORE, D2@BORE, HEXB@HEX, JIC_CONEDIA@DRIVE, LEG_JIC@DRIVE, LEG_ORB@DRIVE, ORB_GRVDIA@DRIVE, ORB_I3@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE, Y@REF, JIC_RELIEFL@DRIVE, RELIEFANG@DRIVE, JIC_THDZ@DRIVE, JIC_LANDL@DRIVE, JIC_SEATL@DRIVE, SEATB@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6801-16-24-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6801-16-24-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6801-16-24-NWO-FG (PARTcommunity / CADENAS, D1@BORE=B1D, D2@BORE=B2D, HEXB@HEX=C, JIC_CONEDIA@DRIVE=AL, LEG_JIC@DRIVE=M, LEG_ORB@DRIVE=M7, ORB_GRVDIA@DRIVE=HT, ORB_I3@DRIVE=GT, THDMAJ_A@DRIVE=B1THD, THDMAJ_B@DRIVE=B2THD, Y@REF=Y; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6801-16-24-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6801-16-24-NWO-FG (PARTcommunity / CADENAS, D1@BORE=B1D, D2@BORE=B2D, HEXB@HEX=C, JIC_CONEDIA@DRIVE=AL, LEG_JIC@DRIVE=M, LEG_ORB@DRIVE=M7, ORB_GRVDIA@DRIVE=HT, ORB_I3@DRIVE=GT, THDMAJ_A@DRIVE=B1THD, THDMAJ_B@DRIVE=B2THD, Y@REF=Y, JIC_RELIEFL@DRIVE=ENDLIB, RELIEFANG@DRIVE=ENDLIB, JIC_THDZ@DRIVE=ENDLIB, JIC_LANDL@DRIVE=ENDLIB, JIC_SEATL@DRIVE=ENDLIB, SEATB@DRIVE=ENDLIB; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
@@ -10217,9 +10289,27 @@
       <c r="D100" t="n">
         <v>1.875</v>
       </c>
+      <c r="E100" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F100" t="n">
+        <v>60</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.5454</v>
+      </c>
       <c r="H100" t="n">
         <v>1.755</v>
       </c>
+      <c r="I100" t="n">
+        <v>0.1298</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0.2482</v>
+      </c>
+      <c r="K100" t="n">
+        <v>37</v>
+      </c>
       <c r="L100" t="n">
         <v>1.3125</v>
       </c>
@@ -10253,12 +10343,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: D1@BORE, D2@BORE, HEXB@HEX, JIC_CONEDIA@DRIVE, LEG_JIC@DRIVE, LEG_ORB@DRIVE, ORB_GRVDIA@DRIVE, ORB_I3@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE, Y@REF] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6801-24-16-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: D1@BORE, D2@BORE, HEXB@HEX, JIC_CONEDIA@DRIVE, LEG_JIC@DRIVE, LEG_ORB@DRIVE, ORB_GRVDIA@DRIVE, ORB_I3@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE, Y@REF, JIC_RELIEFL@DRIVE, RELIEFANG@DRIVE, JIC_THDZ@DRIVE, JIC_LANDL@DRIVE, JIC_SEATL@DRIVE, SEATB@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6801-24-16-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6801-24-16-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6801-24-16-NWO-FG (PARTcommunity / CADENAS, D1@BORE=B1D, D2@BORE=B2D, HEXB@HEX=C, JIC_CONEDIA@DRIVE=AL, LEG_JIC@DRIVE=M, LEG_ORB@DRIVE=M7, ORB_GRVDIA@DRIVE=HT, ORB_I3@DRIVE=GT, THDMAJ_A@DRIVE=B1THD, THDMAJ_B@DRIVE=B2THD, Y@REF=Y; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6801-24-16-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6801-24-16-NWO-FG (PARTcommunity / CADENAS, D1@BORE=B1D, D2@BORE=B2D, HEXB@HEX=C, JIC_CONEDIA@DRIVE=AL, LEG_JIC@DRIVE=M, LEG_ORB@DRIVE=M7, ORB_GRVDIA@DRIVE=HT, ORB_I3@DRIVE=GT, THDMAJ_A@DRIVE=B1THD, THDMAJ_B@DRIVE=B2THD, Y@REF=Y, JIC_RELIEFL@DRIVE=ENDLIB, RELIEFANG@DRIVE=ENDLIB, JIC_THDZ@DRIVE=ENDLIB, JIC_LANDL@DRIVE=ENDLIB, JIC_SEATL@DRIVE=ENDLIB, SEATB@DRIVE=ENDLIB; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
